--- a/data/england/p6_deployment/data_preparation/df_filled_columns.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_filled_columns.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,529 +434,204 @@
           <t>dif_mean_hei_player_miss</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_miss</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>fsjksfhd</t>
+          <t>EqY7Orsg</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>nywy5cp3</t>
+          <t>EcDtwrdn</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ltBAlx0M</t>
+          <t>EJlHkLuh</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>l0Zi1FqS</t>
+          <t>zD1kyMQb</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>tbEWgXy2</t>
+          <t>rw5cZaeB</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>YXAOeg7k</t>
+          <t>zypxSHmo</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bFdtqGNq</t>
+          <t>ABRGMMB5</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SQM1jbV9</t>
+          <t>viJXIvBU</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>d6dJHzU8</t>
+          <t>rPPOK0tI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>r3Wq3yFF</t>
+          <t>v5b6XwQN</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>KQ2pRs2b</t>
+          <t>KMCY9qSa</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>SCsTyaGG</t>
+          <t>2ot8gOsJ</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>KnvLwLo4</t>
+          <t>SSZaQ4Ct</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>K0JghK0c</t>
+          <t>ShJjaSDs</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>WQcQHwPp</t>
+          <t>UiYgHRZP</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>l6f1Na1N</t>
+          <t>n9EQB5cm</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bXkCusHi</t>
+          <t>Y5lic6rf</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>GhdgPLWA</t>
+          <t>tWiaepD6</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>4hy7UG8j</t>
+          <t>Gl6s8NdC</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>8MkyzwoT</t>
+          <t>OE9k61RO</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/df_filled_columns.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_filled_columns.xlsx
@@ -425,214 +425,296 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_hei_player_miss</t>
+          <t>dif_mean_last_60_matches_dangerous_attacks</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_360_matches_red_cards</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_KGP</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>EqY7Orsg</t>
+          <t>A7iT11hT</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.4326663634887347</v>
+      </c>
+      <c r="D2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EcDtwrdn</t>
+          <t>Cl3y4WHa</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.2134746486115841</v>
+      </c>
+      <c r="D3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>EJlHkLuh</t>
+          <t>v3JHq2Wp</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.7557368695388939</v>
+      </c>
+      <c r="D4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>zD1kyMQb</t>
+          <t>WveT5hmm</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.182686166762062</v>
+      </c>
+      <c r="D5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>rw5cZaeB</t>
+          <t>69B375Oi</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.2711311104636549</v>
+      </c>
+      <c r="D6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>zypxSHmo</t>
+          <t>p21q2AnC</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.7557368695388939</v>
+      </c>
+      <c r="D7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>ABRGMMB5</t>
+          <t>EubK3NNG</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>viJXIvBU</t>
+          <t>CEnSxfJ0</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>0.316686939345585</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-1.482645508151752</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-2.562402735252365</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>rPPOK0tI</t>
+          <t>KK9ggF3s</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1.082096005588654</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.182686166762062</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.8297464143993496</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>v5b6XwQN</t>
+          <t>hY71igYg</t>
         </is>
       </c>
       <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>KMCY9qSa</t>
+          <t>CzO2kX26</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>2.409846426622551</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.4326663634887347</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.055873777405409</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>2ot8gOsJ</t>
+          <t>0zTMbytK</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.7540635486273389</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.7557368695388939</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.471001738508735</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>SSZaQ4Ct</t>
+          <t>6HqKvGll</t>
         </is>
       </c>
       <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6980804076868232</v>
+      </c>
+      <c r="D14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>ShJjaSDs</t>
+          <t>nX2mpxRQ</t>
         </is>
       </c>
       <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.5134339900012743</v>
+      </c>
+      <c r="D15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>UiYgHRZP</t>
+          <t>0d4cBEPP</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>-1.526543056913236</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.7557368695388939</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.01161586975343213</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>n9EQB5cm</t>
+          <t>K0RAmBXI</t>
         </is>
       </c>
       <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Y5lic6rf</t>
+          <t>YTzyyYmD</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>tWiaepD6</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>Gl6s8NdC</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>OE9k61RO</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
+        <v>-1.089166447631482</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-1.078807375589053</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.1010079808651672</v>
       </c>
     </row>
   </sheetData>
